--- a/data/trans_dic/AIRE_1_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/AIRE_1_R-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no está dispuesta a pagar para reducir la contaminación del aire (impuesto durante 5 años)</t>
+          <t>Población que no está dispuesta a pagar para reducir la contaminación del aire (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>66,69; 89,34</t>
+          <t>65,46; 89,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>54,6; 80,37</t>
+          <t>55,1; 79,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65,78; 81,6</t>
+          <t>64,83; 82,56</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>69,19; 84,18</t>
+          <t>68,25; 84,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>68,17; 82,7</t>
+          <t>68,1; 83,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70,68; 81,58</t>
+          <t>71,14; 81,3</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57,21; 75,02</t>
+          <t>57,2; 75,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>61,34; 78,47</t>
+          <t>61,21; 78,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63,01; 74,62</t>
+          <t>62,36; 74,8</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>73,76; 90,38</t>
+          <t>73,61; 89,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>63,3; 80,71</t>
+          <t>64,9; 80,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71,7; 83,78</t>
+          <t>71,5; 84,46</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>71,87; 82,41</t>
+          <t>71,67; 82,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>68,13; 77,15</t>
+          <t>67,77; 76,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71,32; 78,33</t>
+          <t>71,32; 78,18</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que no está dispuesta a pagar para reducir la contaminación del aire (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>23780</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17843</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>41623</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>19603; 26653</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>14440; 20891</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>36406; 46361</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>57523</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>74581</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>132104</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>50897; 62696</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>66635; 81952</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>122660; 140178</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>56431</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>82506</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>138936</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>48234; 63973</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>72151; 91963</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>126089; 151243</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>115941</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>106760</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>222701</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>105050; 128146</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>93595; 116479</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>205136; 242317</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>718</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>253675</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>281689</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>535363</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>237616; 272868</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>261692; 296993</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>511856; 561089</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/AIRE_1_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/AIRE_1_R-Edad-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>65,46; 89,0</t>
+          <t>66,48; 89,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>55,1; 79,71</t>
+          <t>53,42; 79,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64,83; 82,56</t>
+          <t>65,0; 81,46</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>68,25; 84,07</t>
+          <t>69,79; 84,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>68,1; 83,76</t>
+          <t>68,0; 82,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71,14; 81,3</t>
+          <t>71,22; 81,62</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57,2; 75,87</t>
+          <t>57,01; 74,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>61,21; 78,01</t>
+          <t>61,85; 77,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>62,36; 74,8</t>
+          <t>62,1; 74,37</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>73,61; 89,8</t>
+          <t>73,86; 90,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>64,9; 80,77</t>
+          <t>64,42; 80,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71,5; 84,46</t>
+          <t>71,8; 84,7</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>71,67; 82,3</t>
+          <t>72,36; 82,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>67,77; 76,91</t>
+          <t>68,07; 77,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71,32; 78,18</t>
+          <t>71,16; 78,17</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19603; 26653</t>
+          <t>19909; 26717</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14440; 20891</t>
+          <t>14000; 20722</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36406; 46361</t>
+          <t>36498; 45740</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>50897; 62696</t>
+          <t>52047; 63052</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>66635; 81952</t>
+          <t>66534; 80769</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>122660; 140178</t>
+          <t>122802; 140735</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>48234; 63973</t>
+          <t>48071; 63113</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>72151; 91963</t>
+          <t>72915; 91462</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>126089; 151243</t>
+          <t>125564; 150385</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>105050; 128146</t>
+          <t>105396; 128766</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>93595; 116479</t>
+          <t>92909; 116046</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>205136; 242317</t>
+          <t>206010; 243005</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>237616; 272868</t>
+          <t>239906; 273005</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>261692; 296993</t>
+          <t>262850; 297538</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>511856; 561089</t>
+          <t>510709; 560991</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/AIRE_1_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/AIRE_1_R-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>73,63%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>66,48; 89,21</t>
+          <t>52,46; 79,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53,42; 79,07</t>
+          <t>65,7; 89,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65,0; 81,46</t>
+          <t>65,11; 80,98</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,12%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>69,79; 84,55</t>
+          <t>68,4; 83,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>68,0; 82,55</t>
+          <t>67,53; 83,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71,22; 81,62</t>
+          <t>70,12; 81,33</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>68,44%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57,01; 74,85</t>
+          <t>61,85; 78,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>61,85; 77,59</t>
+          <t>57,07; 74,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>62,1; 74,37</t>
+          <t>62,83; 74,28</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>75,11%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>73,86; 90,23</t>
+          <t>64,26; 80,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>64,42; 80,47</t>
+          <t>70,06; 82,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71,8; 84,7</t>
+          <t>69,56; 79,87</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>73,24%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>72,36; 82,34</t>
+          <t>68,21; 77,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>68,07; 77,05</t>
+          <t>69,37; 77,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71,16; 78,17</t>
+          <t>70,13; 76,2</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>47</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23780</t>
+          <t>13964</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17843</t>
+          <t>21410</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41623</t>
+          <t>35374</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19909; 26717</t>
+          <t>10994; 16675</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14000; 20722</t>
+          <t>17796; 24239</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>36498; 45740</t>
+          <t>31280; 38906</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>95</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>57523</t>
+          <t>64630</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>74581</t>
+          <t>51143</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>132104</t>
+          <t>115773</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>52047; 63052</t>
+          <t>57724; 70074</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>66534; 80769</t>
+          <t>45720; 56358</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>122802; 140735</t>
+          <t>106647; 123690</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>75</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>56431</t>
+          <t>79364</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>82506</t>
+          <t>55703</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>138936</t>
+          <t>135067</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>48071; 63113</t>
+          <t>69969; 88781</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>72915; 91462</t>
+          <t>48060; 62615</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>125564; 150385</t>
+          <t>124000; 146585</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>115941</t>
+          <t>102781</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>106760</t>
+          <t>93440</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>222701</t>
+          <t>196221</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>105396; 128766</t>
+          <t>89630; 112087</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>92909; 116046</t>
+          <t>85310; 101047</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>206010; 243005</t>
+          <t>181721; 208671</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>346</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>253675</t>
+          <t>260739</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>281689</t>
+          <t>221696</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>535363</t>
+          <t>482435</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>239906; 273005</t>
+          <t>244156; 275967</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>262850; 297538</t>
+          <t>208646; 233782</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>510709; 560991</t>
+          <t>461960; 501963</t>
         </is>
       </c>
     </row>
